--- a/data/trans_bre/IP04D$notiene-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Edad-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,39</t>
+          <t>-4,42; 4,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 6,54</t>
+          <t>-8,06; 5,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 19,11</t>
+          <t>1,92; 20,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 185,93</t>
+          <t>-65,25; 178,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 64,05</t>
+          <t>-44,74; 56,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 471,65</t>
+          <t>7,24; 504,49</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,7</t>
+          <t>-2,86; 2,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 2,59</t>
+          <t>-8,07; 1,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 10,2</t>
+          <t>-2,54; 10,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 120,65</t>
+          <t>-61,94; 114,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 22,15</t>
+          <t>-46,56; 15,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 112,83</t>
+          <t>-19,95; 117,39</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 2,42</t>
+          <t>-6,11; 1,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 2,78</t>
+          <t>-10,4; 1,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -1,46</t>
+          <t>-15,3; -1,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-79,36; 91,54</t>
+          <t>-79,67; 78,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,99; 20,61</t>
+          <t>-49,33; 15,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,56; -7,99</t>
+          <t>-65,8; -7,18</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 6,04</t>
+          <t>-1,68; 5,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 6,69</t>
+          <t>-6,15; 6,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 7,22</t>
+          <t>-8,32; 7,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 294,54</t>
+          <t>-39,54; 254,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 62,95</t>
+          <t>-35,7; 60,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 65,5</t>
+          <t>-46,13; 69,34</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,71</t>
+          <t>-1,92; 1,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,19</t>
+          <t>-4,98; 1,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,53</t>
+          <t>-4,57; 3,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 55,38</t>
+          <t>-38,37; 55,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 8,85</t>
+          <t>-30,4; 9,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 30,14</t>
+          <t>-29,15; 28,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Edad-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 4,15</t>
+          <t>-3,98; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 5,71</t>
+          <t>-7,35; 6,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 20,06</t>
+          <t>1,5; 19,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 178,8</t>
+          <t>-61,29; 193,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 56,66</t>
+          <t>-41,39; 59,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 504,49</t>
+          <t>2,18; 417,15</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,49</t>
+          <t>-2,88; 2,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,91</t>
+          <t>-8,4; 2,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 10,12</t>
+          <t>-2,82; 10,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,94; 114,12</t>
+          <t>-58,46; 104,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 15,83</t>
+          <t>-47,32; 20,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 117,39</t>
+          <t>-21,82; 125,22</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,89</t>
+          <t>-5,46; 1,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 1,93</t>
+          <t>-9,43; 2,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,3; -1,16</t>
+          <t>-14,58; -0,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-79,67; 78,83</t>
+          <t>-77,57; 106,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,33; 15,47</t>
+          <t>-47,89; 17,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,8; -7,18</t>
+          <t>-63,58; 2,33</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 5,37</t>
+          <t>-1,86; 5,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 6,48</t>
+          <t>-6,42; 6,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 7,68</t>
+          <t>-7,88; 7,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 254,8</t>
+          <t>-41,69; 280,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 60,87</t>
+          <t>-38,64; 62,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 69,34</t>
+          <t>-44,66; 61,94</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,75</t>
+          <t>-1,79; 1,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,24</t>
+          <t>-4,82; 1,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,53</t>
+          <t>-4,43; 3,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 55,49</t>
+          <t>-36,55; 51,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 9,73</t>
+          <t>-28,7; 7,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 28,82</t>
+          <t>-28,99; 30,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Edad-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,1</t>
+          <t>9,58</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>133,57%</t>
+          <t>108,47%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 4,42</t>
+          <t>-4,25; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 6,36</t>
+          <t>-7,69; 6,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 19,89</t>
+          <t>-0,17; 19,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-61,29; 193,54</t>
+          <t>-64,29; 185,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,39; 59,82</t>
+          <t>-40,42; 64,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 417,15</t>
+          <t>-9,8; 394,25</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,15</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,43</t>
+          <t>-2,99; 2,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 2,08</t>
+          <t>-7,18; 2,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 10,8</t>
+          <t>-3,64; 7,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 104,93</t>
+          <t>-58,83; 120,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 20,43</t>
+          <t>-44,24; 22,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 125,22</t>
+          <t>-27,98; 100,21</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,55</t>
+          <t>-5,75</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-41,34%</t>
+          <t>-34,9%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,86</t>
+          <t>-5,61; 2,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,36</t>
+          <t>-9,66; 2,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,58; -0,11</t>
+          <t>-12,22; -0,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-77,57; 106,3</t>
+          <t>-79,36; 91,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,89; 17,85</t>
+          <t>-47,99; 20,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 2,33</t>
+          <t>-60,63; 1,67</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 5,3</t>
+          <t>-1,73; 6,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 6,53</t>
+          <t>-6,13; 6,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 7,04</t>
+          <t>-4,57; 4,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 280,74</t>
+          <t>-38,77; 294,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 62,66</t>
+          <t>-34,31; 62,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 61,94</t>
+          <t>-33,93; 54,6</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,87%</t>
+          <t>-2,77%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,6</t>
+          <t>-1,89; 1,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,08</t>
+          <t>-4,68; 1,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,62</t>
+          <t>-3,45; 2,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 51,7</t>
+          <t>-36,56; 55,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 7,65</t>
+          <t>-28,75; 8,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 30,35</t>
+          <t>-24,45; 26,1</t>
         </is>
       </c>
     </row>
